--- a/data/opdracht_template.xlsx
+++ b/data/opdracht_template.xlsx
@@ -372,7 +372,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 09:00:02.585618</t>
+    <t>2024-07-24 09:03:33.382106</t>
   </si>
   <si>
     <t>version</t>
